--- a/stories/arbres/TREE-TMP-001.xlsx
+++ b/stories/arbres/TREE-TMP-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina est dans le salon, avec maman. Le jour, le soleil entre. C'est clair. Maman dit : le jour, le soleil. La nuit, la lune et les étoiles. On fait dodo la nuit. Lina pose le doudou. Papa n'est pas loin. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+          <t>Lina est dans le salon, avec maman. Le jour, le soleil entre. C'est clair. Le jour, le soleil. La nuit, la lune et les étoiles. On fait dodo la nuit. Lina pose le doudou. Papa n'est pas loin. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lina est dans le salon, avec maman. Le jour, le soleil entre. C'est clair.
+maman|Le jour, le soleil.
+narrateur|La nuit, la lune et les étoiles. On fait dodo la nuit. Lina pose le doudou. Papa n'est pas loin. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Lina voit le soleil. Le jour, le soleil. Maman dit : la nuit, ce sera la lune. Dodo la nuit. Lina cligne des yeux. C'est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+          <t>C'est le matin. Lina voit le soleil. Le jour, le soleil. La nuit, ce sera la lune. Dodo la nuit. Lina cligne des yeux. C'est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Lina voit le soleil. Le jour, le soleil.
+maman|La nuit, ce sera la lune. Dodo la nuit.
+narrateur|Lina cligne des yeux. C'est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1863,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour, on voit quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1851,7 +1892,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Lina a dit : le jour, le soleil. La nuit, la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+          <t>Lina Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1993,6 +2034,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Lina
+enfant-f|Le jour, le soleil.
+narrateur|La nuit, la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2227,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2394,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la cuisine. Les chaussures font toc toc. Dans la cuisine, une orange comme un soleil. Le jour. La nuit, la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2589,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2756,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. La lumière est claire. On respire, un, deux. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2923,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3090,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. Des miettes dorment sur la table. On referme le sac. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3257,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3424,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Un chat miaule une fois. On essuie une miette. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3591,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3758,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le jardin. Le papier froisse, chut. Dans le jardin, le soleil chauffe. Le jour. Plus tard, lune, nuit, dodo. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3953,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3982,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lina garde le ballon rouge tout près. Les chaussures font toc toc. On met le doudou près. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina garde le ballon rouge tout près. Les chaussures font toc toc. On met le doudou près. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4120,12 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. Les chaussures font toc toc. On met le doudou près. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4288,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4455,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. La couverture est douce. On lace les chaussures. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4622,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4789,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Une cloche tinte au loin. On met le manteau. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4956,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5123,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la chambre. La couverture est douce. Dans la chambre, le doudou attend. Dodo la nuit. Le jour, le soleil. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5318,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5341,6 +5485,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. Le bois sent le chaud. On boit une gorgée. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5652,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5819,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. Une goutte tombe, ploc. On feuillette le livre. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5986,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6153,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Le savon sent la fleur. On referme le livre. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6320,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6349,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, la lumière est douce. Encore le jour. Le soleil. Maman dit : plus tard, la lune, la nuit. Dodo la nuit. Lina s'étire. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+          <t>Après la sieste, la lumière est douce. Encore le jour. Le soleil. Plus tard, la lune, la nuit. Dodo la nuit. Lina s'étire. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6487,13 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, la lumière est douce. Encore le jour. Le soleil.
+maman|Plus tard, la lune, la nuit. Dodo la nuit.
+narrateur|Lina s'étire. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6670,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|La nuit, on voit quoi ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6843,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Soleil le jour. Lune la nuit. Lina fera dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7034,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7201,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la cuisine. Le papier froisse, chut. Ça sent le pain. Encore le jour, le soleil. La lune viendra la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7396,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7425,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lina garde le ballon rouge tout près. Le tissu est tout doux. On pose le ballon. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina garde le ballon rouge tout près. Le tissu est tout doux. On pose le ballon. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7563,12 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. Le tissu est tout doux. On pose le ballon. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7731,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7898,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. Une cuillère tinte. On secoue le sable. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8065,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8232,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Le sable est tiède. On caresse le tissu. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8399,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8191,7 +8428,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le jardin. Un oiseau chante tout près. Une feuille tombe. Le jour. Maman dit : dodo la nuit, avec la lune. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+          <t>Lina va vers le jardin. Un oiseau chante tout près. Une feuille tombe. Le jour. Dodo la nuit, avec la lune. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8329,6 +8566,13 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le jardin. Un oiseau chante tout près. Une feuille tombe. Le jour.
+maman|Dodo la nuit, avec la lune.
+narrateur|Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8763,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8681,6 +8930,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. Un rire court, tout petit. On tend la main. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9097,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9264,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. Le papier froisse, chut. On chante un petit air. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9431,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9598,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. L'herbe chatouille le mollet. On compte jusqu'à trois. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9765,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9932,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la chambre. Un oiseau chante tout près. Le lit est prêt. Lina pense à la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10127,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9867,7 +10156,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lina garde le ballon rouge tout près. Un pigeon roucoule. On montre du doigt. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina garde le ballon rouge tout près. Un pigeon roucoule. On montre du doigt. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10005,6 +10294,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. Un pigeon roucoule. On montre du doigt. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10462,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10629,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. La fenêtre vibre un peu. On range la chaise. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10796,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10963,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Le lait est froid dans le verre. On range un objet. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11130,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11297,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le soleil s'en va. Maman montre la fenêtre. Bientôt la lune. La nuit. On fait dodo la nuit. Lina bâille. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11157,6 +11482,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Quand on fait dodo ?</t>
         </is>
       </c>
     </row>
@@ -11325,6 +11655,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Maman confirme. Dodo la nuit. Le soleil, c'est le jour. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11511,6 +11846,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11673,6 +12013,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la cuisine. Un pain croustille. Lina boit de l'eau. Le soleil brille. Le jour. La nuit, dodo. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11863,6 +12208,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12025,6 +12375,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. La corde du sac est rêche. On se tient la main. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12187,6 +12542,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12349,6 +12709,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. Le savon mousse entre les doigts. On dit merci. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12511,6 +12876,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12673,6 +13043,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Un ruisseau chante. On souffle doucement. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12835,6 +13210,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12997,6 +13377,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le jardin. Le savon glisse. Le vent est doux. Jour, soleil. Nuit, lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13187,6 +13572,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13211,7 +13601,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Lina garde le ballon rouge tout près. La laine gratte un peu. On écoute jusqu'au bout. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina garde le ballon rouge tout près. La laine gratte un peu. On écoute jusqu'au bout. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13349,6 +13739,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. La laine gratte un peu. On écoute jusqu'au bout. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13511,6 +13907,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13673,6 +14074,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. Un pain croustille. On attend son tour. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13835,6 +14241,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13997,6 +14408,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Le savon glisse. On sourit ensemble. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14159,6 +14575,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14183,7 +14604,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers la chambre. La fenêtre vibre un peu. Lina pose la tête. Maman dit : bientôt dodo la nuit. La lune. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+          <t>Lina va vers la chambre. La fenêtre vibre un peu. Lina pose la tête. Bientôt dodo la nuit. La lune. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14321,6 +14742,13 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la chambre. La fenêtre vibre un peu. Lina pose la tête.
+maman|Bientôt dodo la nuit.
+narrateur|La lune. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14511,6 +14939,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14673,6 +15106,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le ballon rouge tout près. Une plume vole. On pose les pieds par terre. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14835,6 +15273,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14997,6 +15440,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le seau bleu tout près. Le banc est lisse. On parle tout bas. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15159,6 +15607,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15321,6 +15774,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina garde le doudou tout près. Un grelot sonne. On range les jouets. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15483,6 +15941,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15501,7 +15964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15518,6 +15981,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-001.xlsx
+++ b/stories/arbres/TREE-TMP-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|La nuit, la lune et les étoiles. On fait dodo la nuit. Lina pose le doudou. Papa n'est pas loin. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Lina cligne des yeux. C'est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Le jour, on voit quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
 narrateur|La nuit, la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Lina va vers la cuisine. Les chaussures font toc toc. Dans la cuisine, une orange comme un soleil. Le jour. La nuit, la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2594,6 +2606,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2761,6 +2774,7 @@
           <t>narrateur|Lina garde le ballon rouge tout près. La lumière est claire. On respire, un, deux. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2928,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3095,6 +3110,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. Des miettes dorment sur la table. On referme le sac. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3262,6 +3278,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3429,6 +3446,7 @@
           <t>narrateur|Lina garde le doudou tout près. Un chat miaule une fois. On essuie une miette. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3596,6 +3614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3763,6 +3782,7 @@
           <t>narrateur|Lina va vers le jardin. Le papier froisse, chut. Dans le jardin, le soleil chauffe. Le jour. Plus tard, lune, nuit, dodo. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3958,6 +3978,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4126,6 +4147,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4293,6 +4315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4460,6 +4483,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. La couverture est douce. On lace les chaussures. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4627,6 +4651,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4794,6 +4819,7 @@
           <t>narrateur|Lina garde le doudou tout près. Une cloche tinte au loin. On met le manteau. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4961,6 +4987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5128,6 +5155,7 @@
           <t>narrateur|Lina va vers la chambre. La couverture est douce. Dans la chambre, le doudou attend. Dodo la nuit. Le jour, le soleil. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5323,6 +5351,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5490,6 +5519,7 @@
           <t>narrateur|Lina garde le ballon rouge tout près. Le bois sent le chaud. On boit une gorgée. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5657,6 +5687,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5824,6 +5855,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. Une goutte tombe, ploc. On feuillette le livre. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5991,6 +6023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6158,6 +6191,7 @@
           <t>narrateur|Lina garde le doudou tout près. Le savon sent la fleur. On referme le livre. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6325,6 +6359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6494,6 +6529,7 @@
 narrateur|Lina s'étire. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6677,6 +6713,7 @@
           <t>narrateur|La nuit, on voit quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6848,6 +6885,7 @@
           <t>narrateur|Soleil le jour. Lune la nuit. Lina fera dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7039,6 +7077,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7206,6 +7245,7 @@
           <t>narrateur|Lina va vers la cuisine. Le papier froisse, chut. Ça sent le pain. Encore le jour, le soleil. La lune viendra la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7401,6 +7441,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. Une cuillère tinte. On secoue le sable. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Lina garde le doudou tout près. Le sable est tiède. On caresse le tissu. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8573,6 +8620,7 @@
 narrateur|Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8768,6 +8816,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8935,6 +8984,7 @@
           <t>narrateur|Lina garde le ballon rouge tout près. Un rire court, tout petit. On tend la main. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9102,6 +9152,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9269,6 +9320,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. Le papier froisse, chut. On chante un petit air. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9436,6 +9488,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9603,6 +9656,7 @@
           <t>narrateur|Lina garde le doudou tout près. L'herbe chatouille le mollet. On compte jusqu'à trois. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9770,6 +9824,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9937,6 +9992,7 @@
           <t>narrateur|Lina va vers la chambre. Un oiseau chante tout près. Le lit est prêt. Lina pense à la lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10132,6 +10188,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10300,6 +10357,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10467,6 +10525,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10634,6 +10693,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. La fenêtre vibre un peu. On range la chaise. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10801,6 +10861,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10968,6 +11029,7 @@
           <t>narrateur|Lina garde le doudou tout près. Le lait est froid dans le verre. On range un objet. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11135,6 +11197,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11302,6 +11365,7 @@
           <t>narrateur|C'est le soir. Le soleil s'en va. Maman montre la fenêtre. Bientôt la lune. La nuit. On fait dodo la nuit. Lina bâille. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11489,6 +11553,7 @@
           <t>narrateur|Quand on fait dodo ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11660,6 +11725,7 @@
           <t>narrateur|Maman confirme. Dodo la nuit. Le soleil, c'est le jour. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11851,6 +11917,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12018,6 +12085,7 @@
           <t>narrateur|Lina va vers la cuisine. Un pain croustille. Lina boit de l'eau. Le soleil brille. Le jour. La nuit, dodo. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12213,6 +12281,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12380,6 +12449,7 @@
           <t>narrateur|Lina garde le ballon rouge tout près. La corde du sac est rêche. On se tient la main. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12547,6 +12617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12714,6 +12785,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. Le savon mousse entre les doigts. On dit merci. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12881,6 +12953,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13048,6 +13121,7 @@
           <t>narrateur|Lina garde le doudou tout près. Un ruisseau chante. On souffle doucement. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13215,6 +13289,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13382,6 +13457,7 @@
           <t>narrateur|Lina va vers le jardin. Le savon glisse. Le vent est doux. Jour, soleil. Nuit, lune. Dodo la nuit. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13577,6 +13653,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13745,6 +13822,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13912,6 +13990,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14079,6 +14158,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. Un pain croustille. On attend son tour. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14246,6 +14326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14413,6 +14494,7 @@
           <t>narrateur|Lina garde le doudou tout près. Le savon glisse. On sourit ensemble. Le jour, le soleil. La nuit, la lune. Dodo la nuit. On bâille un peu. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14580,6 +14662,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14749,6 +14832,7 @@
 narrateur|La lune. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14944,6 +15028,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15111,6 +15196,7 @@
           <t>narrateur|Lina garde le ballon rouge tout près. Une plume vole. On pose les pieds par terre. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le ciel est clair. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15278,6 +15364,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15445,6 +15532,7 @@
           <t>narrateur|Lina garde le seau bleu tout près. Le banc est lisse. On parle tout bas. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Les étoiles viendront. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15612,6 +15700,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15779,6 +15868,7 @@
           <t>narrateur|Lina garde le doudou tout près. Un grelot sonne. On range les jouets. Le jour, le soleil. La nuit, la lune. Dodo la nuit. Le doudou est prêt. Le jour, le soleil. La nuit, la lune. On fait dodo la nuit. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15946,6 +16036,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15964,7 +16055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15988,6 +16079,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16189,6 +16294,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
